--- a/Dataset/updateexcel/nodes_iter_9.xlsx
+++ b/Dataset/updateexcel/nodes_iter_9.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,10 +443,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -454,13 +454,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="b">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -468,13 +468,13 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -488,7 +488,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -502,7 +502,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -516,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -544,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
@@ -558,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -614,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
@@ -622,13 +622,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B15" t="b">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
@@ -636,505 +636,15 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B16" t="b">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>25</v>
-      </c>
-      <c r="B17" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="D17" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D19" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D20" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="D21" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D22" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D23" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="b">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D26" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="b">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D27" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="b">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="D28" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="b">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="D29" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="b">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D30" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="b">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="D31" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="b">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="D32" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="b">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="D33" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="b">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D34" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="b">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="D35" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="b">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="D36" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="b">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D37" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="b">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D38" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="b">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D39" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="b">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D40" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="b">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D41" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="b">
-        <v>0</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D42" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="b">
-        <v>0</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D43" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="b">
-        <v>0</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D44" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="b">
-        <v>0</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D45" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="b">
-        <v>0</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D46" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="b">
-        <v>0</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D47" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="b">
-        <v>0</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D48" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="b">
-        <v>0</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D49" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="D50" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="b">
-        <v>0</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D51" t="n">
         <v>9</v>
       </c>
     </row>
